--- a/data/tags/אלבומים חדשים/global/2026-06-week02/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/2026-06-week02/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יובל דיין - יובל דיין לייב</v>
+        <v>נינט טייב – אני נינה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-11</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24475&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%a0%d7%99%d7%a0%d7%98-%d7%98%d7%99%d7%99%d7%91-%d7%90%d7%a0%d7%99-%d7%a0%d7%99%d7%a0%d7%94/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>20:02</v>
+        <v>"אני נינה" של נינט טייב מהווה צומת דרכים מכונן בקריירה של אחת הזמרות-יוצרות הבולטות בישראל. הטקסטים של שירי האלבום מתארים תהליך של פירוק והרכבה מחדש, שבו נינט מתרחקת מהדימוי הציבורי הישן שלה ומגדירה את זהותה מחדש כאמנית חופשיה, בוגרת, רוקיסטית</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יובל דיין - יובל דיין לייב</v>
+        <v>נינט טייב – אני נינה</v>
       </c>
     </row>
   </sheetData>
